--- a/Тестирование API admin и user v 2.0.xlsx
+++ b/Тестирование API admin и user v 2.0.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="259">
   <si>
     <t>Auth</t>
   </si>
@@ -799,10 +799,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="42" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -827,15 +827,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF800080"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -856,24 +865,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -881,29 +874,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -918,19 +888,19 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="Calibri"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -948,8 +918,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -963,11 +941,33 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -998,7 +998,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1010,13 +1010,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1028,37 +1046,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1076,19 +1076,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1100,7 +1100,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1112,73 +1178,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1210,6 +1210,17 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -1225,28 +1236,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1266,15 +1260,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -1289,157 +1274,172 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="24" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1468,9 +1468,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -18686,7 +18683,7 @@
       <c r="D38" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="F38" s="12" t="s">
+      <c r="F38" s="9" t="s">
         <v>78</v>
       </c>
       <c r="G38" s="4" t="s">
@@ -18881,7 +18878,7 @@
       <c r="D51" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="F51" s="12" t="s">
+      <c r="F51" s="9" t="s">
         <v>107</v>
       </c>
       <c r="H51" s="10" t="s">
@@ -18984,17 +18981,20 @@
         <v>122</v>
       </c>
     </row>
-    <row r="59" spans="1:4">
-      <c r="A59" s="7" t="s">
+    <row r="59" s="2" customFormat="1" spans="1:8">
+      <c r="A59" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="B59" s="7" t="s">
+      <c r="B59" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C59" s="7" t="s">
+      <c r="C59" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="D59" s="7" t="s">
+      <c r="D59" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H59" s="6" t="s">
         <v>125</v>
       </c>
     </row>
@@ -19368,100 +19368,100 @@
       </c>
     </row>
     <row r="88" spans="1:4">
-      <c r="A88" s="13" t="s">
+      <c r="A88" s="12" t="s">
         <v>203</v>
       </c>
-      <c r="B88" s="13" t="s">
+      <c r="B88" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C88" s="13" t="s">
+      <c r="C88" s="12" t="s">
         <v>204</v>
       </c>
-      <c r="D88" s="13" t="s">
+      <c r="D88" s="12" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="89" spans="1:4">
-      <c r="A89" s="13" t="s">
+      <c r="A89" s="12" t="s">
         <v>206</v>
       </c>
-      <c r="B89" s="13" t="s">
+      <c r="B89" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C89" s="13" t="s">
+      <c r="C89" s="12" t="s">
         <v>204</v>
       </c>
-      <c r="D89" s="13" t="s">
+      <c r="D89" s="12" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="90" spans="1:4">
-      <c r="A90" s="13" t="s">
+      <c r="A90" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="B90" s="13" t="s">
+      <c r="B90" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C90" s="13" t="s">
+      <c r="C90" s="12" t="s">
         <v>209</v>
       </c>
-      <c r="D90" s="13" t="s">
+      <c r="D90" s="12" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="91" spans="1:4">
-      <c r="A91" s="13" t="s">
+      <c r="A91" s="12" t="s">
         <v>211</v>
       </c>
-      <c r="B91" s="13" t="s">
+      <c r="B91" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="C91" s="13" t="s">
+      <c r="C91" s="12" t="s">
         <v>209</v>
       </c>
-      <c r="D91" s="13" t="s">
+      <c r="D91" s="12" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="92" spans="1:4">
-      <c r="A92" s="13" t="s">
+      <c r="A92" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="B92" s="13" t="s">
+      <c r="B92" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="C92" s="13" t="s">
+      <c r="C92" s="12" t="s">
         <v>209</v>
       </c>
-      <c r="D92" s="13" t="s">
+      <c r="D92" s="12" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="93" spans="1:4">
-      <c r="A93" s="13" t="s">
+      <c r="A93" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="B93" s="13" t="s">
+      <c r="B93" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="C93" s="13" t="s">
+      <c r="C93" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="D93" s="13" t="s">
+      <c r="D93" s="12" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="94" spans="1:4">
-      <c r="A94" s="13" t="s">
+      <c r="A94" s="12" t="s">
         <v>217</v>
       </c>
-      <c r="B94" s="13" t="s">
+      <c r="B94" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="C94" s="13" t="s">
+      <c r="C94" s="12" t="s">
         <v>218</v>
       </c>
-      <c r="D94" s="13" t="s">
+      <c r="D94" s="12" t="s">
         <v>219</v>
       </c>
     </row>
@@ -19471,142 +19471,142 @@
       </c>
     </row>
     <row r="97" spans="1:4">
-      <c r="A97" s="13" t="s">
+      <c r="A97" s="12" t="s">
         <v>221</v>
       </c>
-      <c r="B97" s="13" t="s">
+      <c r="B97" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C97" s="13" t="s">
+      <c r="C97" s="12" t="s">
         <v>222</v>
       </c>
-      <c r="D97" s="13" t="s">
+      <c r="D97" s="12" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="98" spans="1:4">
-      <c r="A98" s="13" t="s">
+      <c r="A98" s="12" t="s">
         <v>224</v>
       </c>
-      <c r="B98" s="13" t="s">
+      <c r="B98" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C98" s="13" t="s">
+      <c r="C98" s="12" t="s">
         <v>225</v>
       </c>
-      <c r="D98" s="13" t="s">
+      <c r="D98" s="12" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="99" spans="1:4">
-      <c r="A99" s="13" t="s">
+      <c r="A99" s="12" t="s">
         <v>227</v>
       </c>
-      <c r="B99" s="13" t="s">
+      <c r="B99" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C99" s="13" t="s">
+      <c r="C99" s="12" t="s">
         <v>228</v>
       </c>
-      <c r="D99" s="13" t="s">
+      <c r="D99" s="12" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="100" spans="1:4">
-      <c r="A100" s="13" t="s">
+      <c r="A100" s="12" t="s">
         <v>230</v>
       </c>
-      <c r="B100" s="13" t="s">
+      <c r="B100" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C100" s="13" t="s">
+      <c r="C100" s="12" t="s">
         <v>228</v>
       </c>
-      <c r="D100" s="13" t="s">
+      <c r="D100" s="12" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="101" spans="1:4">
-      <c r="A101" s="13" t="s">
+      <c r="A101" s="12" t="s">
         <v>232</v>
       </c>
-      <c r="B101" s="13" t="s">
+      <c r="B101" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C101" s="13" t="s">
+      <c r="C101" s="12" t="s">
         <v>233</v>
       </c>
-      <c r="D101" s="13" t="s">
+      <c r="D101" s="12" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="102" spans="1:4">
-      <c r="A102" s="13" t="s">
+      <c r="A102" s="12" t="s">
         <v>235</v>
       </c>
-      <c r="B102" s="13" t="s">
+      <c r="B102" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="C102" s="13" t="s">
+      <c r="C102" s="12" t="s">
         <v>233</v>
       </c>
-      <c r="D102" s="13" t="s">
+      <c r="D102" s="12" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="103" spans="1:4">
-      <c r="A103" s="13" t="s">
+      <c r="A103" s="12" t="s">
         <v>237</v>
       </c>
-      <c r="B103" s="13" t="s">
+      <c r="B103" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C103" s="13" t="s">
+      <c r="C103" s="12" t="s">
         <v>238</v>
       </c>
-      <c r="D103" s="13" t="s">
+      <c r="D103" s="12" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="104" spans="1:4">
-      <c r="A104" s="13" t="s">
+      <c r="A104" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="B104" s="13" t="s">
+      <c r="B104" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C104" s="13" t="s">
+      <c r="C104" s="12" t="s">
         <v>238</v>
       </c>
-      <c r="D104" s="13" t="s">
+      <c r="D104" s="12" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="105" spans="1:4">
-      <c r="A105" s="13" t="s">
+      <c r="A105" s="12" t="s">
         <v>242</v>
       </c>
-      <c r="B105" s="13" t="s">
+      <c r="B105" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C105" s="13" t="s">
+      <c r="C105" s="12" t="s">
         <v>243</v>
       </c>
-      <c r="D105" s="13" t="s">
+      <c r="D105" s="12" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="106" spans="1:4">
-      <c r="A106" s="13" t="s">
+      <c r="A106" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="B106" s="13" t="s">
+      <c r="B106" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="C106" s="13" t="s">
+      <c r="C106" s="12" t="s">
         <v>243</v>
       </c>
-      <c r="D106" s="13" t="s">
+      <c r="D106" s="12" t="s">
         <v>246</v>
       </c>
     </row>
@@ -19616,19 +19616,19 @@
       </c>
     </row>
     <row r="109" spans="1:5">
-      <c r="A109" s="13" t="s">
+      <c r="A109" s="12" t="s">
         <v>248</v>
       </c>
-      <c r="B109" s="13" t="s">
+      <c r="B109" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C109" s="13" t="s">
+      <c r="C109" s="12" t="s">
         <v>249</v>
       </c>
-      <c r="D109" s="13" t="s">
+      <c r="D109" s="12" t="s">
         <v>250</v>
       </c>
-      <c r="E109" s="13"/>
+      <c r="E109" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Тестирование API admin и user v 2.0.xlsx
+++ b/Тестирование API admin и user v 2.0.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="253">
   <si>
     <t>Auth</t>
   </si>
@@ -442,9 +442,6 @@
     <t>/admin/tickets/{ticket_id}/department</t>
   </si>
   <si>
-    <t>change_ticket_department_admin_tickets__ticket_id__department_patch</t>
-  </si>
-  <si>
     <t>Принятие заявки</t>
   </si>
   <si>
@@ -478,6 +475,9 @@
     <t>/admin/tickets/{ticket_id}/schedule</t>
   </si>
   <si>
+    <t>Можно указать планиуемую дату раньше текущей. Статус меняется</t>
+  </si>
+  <si>
     <t>schedule_ticket_admin_tickets__ticket_id__schedule_patch</t>
   </si>
   <si>
@@ -485,6 +485,9 @@
   </si>
   <si>
     <t>/admin/tickets/{ticket_id}/executor</t>
+  </si>
+  <si>
+    <t>Можно назначить исполнителя из другого отдела, не та к которому принадлжит заявка, статус меняется</t>
   </si>
   <si>
     <t>assign_executor_admin_tickets__ticket_id__executor_patch</t>
@@ -19003,7 +19006,9 @@
       <c r="C61" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="D61" s="5"/>
+      <c r="D61" s="5" t="s">
+        <v>4</v>
+      </c>
       <c r="H61" s="5" t="s">
         <v>131</v>
       </c>
@@ -19018,392 +19023,421 @@
       <c r="C62" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="D62" s="5"/>
+      <c r="D62" s="5" t="s">
+        <v>4</v>
+      </c>
       <c r="H62" s="5" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="63" spans="1:4">
-      <c r="A63" s="6" t="s">
+    <row r="63" s="2" customFormat="1" spans="1:8">
+      <c r="A63" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="B63" s="6" t="s">
+      <c r="B63" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C63" s="6" t="s">
+      <c r="C63" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="D63" s="6" t="s">
+      <c r="D63" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="H63" s="10" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="64" spans="1:4">
-      <c r="A64" s="6" t="s">
+    <row r="64" s="1" customFormat="1" spans="1:8">
+      <c r="A64" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="B64" s="6" t="s">
+      <c r="B64" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="C64" s="6" t="s">
+      <c r="C64" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="D64" s="6" t="s">
+      <c r="D64" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="H64" s="5" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="65" spans="1:4">
-      <c r="A65" s="6" t="s">
+    <row r="65" s="1" customFormat="1" spans="1:4">
+      <c r="A65" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="B65" s="6" t="s">
+      <c r="B65" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="C65" s="6" t="s">
+      <c r="C65" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="D65" s="6" t="s">
+      <c r="D65" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="66" s="1" customFormat="1" spans="1:8">
+      <c r="A66" s="5" t="s">
         <v>142</v>
       </c>
+      <c r="B66" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="H66" s="5" t="s">
+        <v>144</v>
+      </c>
     </row>
-    <row r="66" spans="1:4">
-      <c r="A66" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="B66" s="6" t="s">
+    <row r="67" s="2" customFormat="1" spans="1:8">
+      <c r="A67" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="B67" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="C66" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="D66" s="6" t="s">
-        <v>145</v>
+      <c r="C67" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D67" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="H67" s="10" t="s">
+        <v>147</v>
       </c>
     </row>
-    <row r="67" spans="1:4">
-      <c r="A67" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="B67" s="6" t="s">
+    <row r="68" s="1" customFormat="1" spans="1:8">
+      <c r="A68" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="B68" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="C67" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="D67" s="6" t="s">
-        <v>148</v>
+      <c r="C68" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D68" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="H68" s="5" t="s">
+        <v>150</v>
       </c>
     </row>
-    <row r="68" spans="1:4">
-      <c r="A68" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="B68" s="6" t="s">
+    <row r="69" s="3" customFormat="1" spans="1:8">
+      <c r="A69" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="B69" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="C68" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="D68" s="6" t="s">
-        <v>151</v>
+      <c r="C69" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="D69" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="H69" s="9" t="s">
+        <v>154</v>
       </c>
     </row>
-    <row r="69" spans="1:4">
-      <c r="A69" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="B69" s="6" t="s">
+    <row r="70" s="3" customFormat="1" spans="1:8">
+      <c r="A70" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="B70" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="C69" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="D69" s="6" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4">
-      <c r="A70" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C70" s="6" t="s">
+      <c r="C70" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="D70" s="6" t="s">
+      <c r="D70" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="F70" s="3" t="s">
         <v>157</v>
+      </c>
+      <c r="H70" s="9" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B71" s="6" t="s">
         <v>62</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B72" s="6" t="s">
         <v>62</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B73" s="6" t="s">
         <v>62</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B74" s="6" t="s">
         <v>62</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B75" s="6" t="s">
         <v>62</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>62</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B77" s="6" t="s">
         <v>62</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B78" s="6" t="s">
         <v>62</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B79" s="6" t="s">
         <v>62</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B80" s="6" t="s">
         <v>62</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B81" s="6" t="s">
         <v>62</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B82" s="6" t="s">
         <v>62</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B83" s="6" t="s">
         <v>62</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B84" s="6" t="s">
         <v>62</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B85" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="11" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B88" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C88" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D88" s="11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="11" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B89" s="11" t="s">
         <v>2</v>
       </c>
       <c r="C89" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D89" s="11" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="11" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B90" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C90" s="11" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D90" s="11" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B91" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C91" s="11" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D91" s="11" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -19414,202 +19448,202 @@
         <v>31</v>
       </c>
       <c r="C92" s="11" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D92" s="11" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="11" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B93" s="11" t="s">
         <v>62</v>
       </c>
       <c r="C93" s="11" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D93" s="11" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="11" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B94" s="11" t="s">
         <v>62</v>
       </c>
       <c r="C94" s="11" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D94" s="11" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="96" spans="1:1">
       <c r="A96" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="11" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B97" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C97" s="11" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D97" s="11" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="11" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B98" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C98" s="11" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D98" s="11" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="11" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B99" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C99" s="11" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D99" s="11" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="11" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B100" s="11" t="s">
         <v>2</v>
       </c>
       <c r="C100" s="11" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D100" s="11" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="11" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B101" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C101" s="11" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D101" s="11" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="11" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B102" s="11" t="s">
         <v>31</v>
       </c>
       <c r="C102" s="11" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D102" s="11" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="11" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B103" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C103" s="11" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D103" s="11" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="11" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B104" s="11" t="s">
         <v>2</v>
       </c>
       <c r="C104" s="11" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D104" s="11" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="11" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B105" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C105" s="11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D105" s="11" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="11" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B106" s="11" t="s">
         <v>31</v>
       </c>
       <c r="C106" s="11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D106" s="11" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="108" spans="1:1">
       <c r="A108" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="11" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B109" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C109" s="11" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D109" s="11" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E109" s="11"/>
     </row>

--- a/Тестирование API admin и user v 2.0.xlsx
+++ b/Тестирование API admin и user v 2.0.xlsx
@@ -780,10 +780,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="42" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -808,8 +808,63 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -823,46 +878,45 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -877,76 +931,22 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="Calibri"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -985,48 +985,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1039,7 +997,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1051,37 +1099,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1093,25 +1141,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1123,49 +1153,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1183,31 +1183,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1238,11 +1214,41 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1262,17 +1268,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1281,148 +1281,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Тестирование API admin и user v 2.0.xlsx
+++ b/Тестирование API admin и user v 2.0.xlsx
@@ -780,9 +780,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="42" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
   <fonts count="22">
@@ -808,9 +808,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -824,9 +823,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -840,15 +838,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="Calibri"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF0000FF"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -856,74 +856,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -939,14 +871,82 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -985,43 +985,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1033,37 +1045,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1081,7 +1069,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1093,49 +1135,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1147,25 +1153,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1184,6 +1184,30 @@
       <top/>
       <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1214,6 +1238,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -1232,45 +1271,6 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
@@ -1281,127 +1281,127 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1413,16 +1413,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
